--- a/docs/HCM_Academy_QA_Review.xlsx
+++ b/docs/HCM_Academy_QA_Review.xlsx
@@ -9663,13 +9663,13 @@
       <c r="K56" s="8" t="inlineStr">
         <is>
           <t>- Which Oracle absence types Vanderbilt uses for FMLA, TMLA (TPLA), and FMLA running at the same time as state leave, and who enters intermittent occurrences, must be confirmed.
-- Vanderbilt's leave process is pending review by Sheila, the Leave SME.
+- Vanderbilt's leave process is pending review by the Leave SME.
 - Oracle absence types Vanderbilt uses for FMLA, TMLA/TPLA, and concurrent FMLA and state leave
 - Who enters intermittent occurrences (HCM, employee, or Leave team) and how often
 - Whether FMLA is tracked in hours or days at Vanderbilt and which 12-month period method is used
 - Current TPLA eligibility rules and leave length in T.C.A. 4-21-408 (confirm with Leave SME or legal)
 - Whether a continuous FMLA/TMLA leave also requires a leave status change in Change Assignment
-- Sheila (Leave SME) review of the full FMLA/TMLA process</t>
+- The Leave SME (Leave SME) review of the full FMLA/TMLA process</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr"/>
@@ -9792,12 +9792,12 @@
       <c r="K58" s="8" t="inlineStr">
         <is>
           <t>- Vanderbilt's approval routing for each absence type (who approves, whether HR or the Leave team is in the chain, what happens if an approver does not act) must be confirmed.
-- Vanderbilt's leave process is pending review by Sheila, the Leave SME.
+- Vanderbilt's leave process is pending review by the Leave SME.
 - Approval routing for each Vanderbilt absence type (approvers, Leave team involvement)
 - Whether absence approvals expire or escalate, and the action on expiry
 - Whether HCMs can see and act on requests for their area in the notifications bell
 - Whether withdrawals of approved absences require approval at Vanderbilt
-- Sheila (Leave SME) review of the full workflow</t>
+- The Leave SME (Leave SME) review of the full workflow</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr"/>
@@ -9865,11 +9865,11 @@
       <c r="K59" s="8" t="inlineStr">
         <is>
           <t>- Which quick actions HCMs see under Our Workforce, and whether HCMs approve exempt time off or only managers do, must be confirmed on screen.
-- Vanderbilt's leave process is pending review by Sheila, the Leave SME.
+- Vanderbilt's leave process is pending review by the Leave SME.
 - Which absence quick actions (Add Absence, Existing Absences, Absence Balance) HCMs see under Our Workforce &gt; Quick Actions
 - Absence types and plans available to exempt employees (vacation, sick, etc.)
 - Whether exempt time off can be entered in partial days or hours
-- Sheila (Leave SME) review of the full process</t>
+- The Leave SME (Leave SME) review of the full process</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
